--- a/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{ED24C437-66CF-4628-A32D-BDE23416ECFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0210792F-21D7-41BE-A902-F716E50CFB09}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{ED24C437-66CF-4628-A32D-BDE23416ECFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F5301D3-CB56-4D57-9BB9-979A30387459}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E31E48B5-560A-4B75-91E6-47685E8599C6}"/>
   </bookViews>
@@ -752,127 +752,127 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1193,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734DFF48-CF26-42BE-975B-28ABE9130CF9}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.88671875" style="2" customWidth="1"/>
@@ -1227,13 +1227,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="65"/>
+      <c r="A1" s="27"/>
     </row>
     <row r="2" spans="1:27" ht="17.399999999999999">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="63"/>
+      <c r="B2" s="25"/>
       <c r="C2" s="18"/>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
@@ -1259,7 +1259,7 @@
       <c r="AA2" s="4"/>
     </row>
     <row r="3" spans="1:27" ht="15.6">
-      <c r="A3" s="64"/>
+      <c r="A3" s="26"/>
       <c r="C3" s="18"/>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -1285,10 +1285,7 @@
       <c r="AA3" s="4"/>
     </row>
     <row r="4" spans="1:27" ht="15.6">
-      <c r="A4" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="34"/>
+      <c r="A4" s="26"/>
       <c r="C4" s="18"/>
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
@@ -1313,14 +1310,15 @@
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
     </row>
-    <row r="5" spans="1:27" ht="15" thickBot="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="4"/>
+    <row r="5" spans="1:27" ht="15.6">
+      <c r="A5" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="64"/>
+      <c r="C5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="19"/>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5"/>
@@ -1341,259 +1339,289 @@
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
     </row>
-    <row r="6" spans="1:27" ht="15" thickTop="1">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:27" ht="15" thickBot="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="4"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+    </row>
+    <row r="7" spans="1:27" ht="15" thickTop="1">
+      <c r="A7" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B7" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C7" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D7" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E7" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F7" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G7" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H7" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I7" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J7" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="25" t="s">
+      <c r="K7" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M7" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="38" t="s">
+      <c r="N7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="O6" s="38" t="s">
+      <c r="O7" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="54" t="s">
+      <c r="P7" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="59" t="s">
+      <c r="Q7" s="51"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="U6" s="60"/>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="62" t="s">
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="Z6" s="28" t="s">
+      <c r="Z7" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="AA6" s="31" t="s">
+      <c r="AA7" s="35" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15" thickBot="1">
-      <c r="A7" s="36"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="57"/>
-      <c r="P7" s="43" t="s">
+    <row r="8" spans="1:27" ht="15" thickBot="1">
+      <c r="A8" s="66"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="Q7" s="45" t="s">
+      <c r="Q8" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="47" t="s">
+      <c r="R8" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="48" t="s">
+      <c r="S8" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="T7" s="50" t="s">
+      <c r="T8" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="U7" s="51" t="s">
+      <c r="U8" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="32"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="62"/>
+      <c r="AA8" s="36"/>
     </row>
-    <row r="8" spans="1:27" ht="43.8" thickBot="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="16" t="s">
+    <row r="9" spans="1:27" ht="43.8" thickBot="1">
+      <c r="A9" s="46"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="57"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="V8" s="17" t="s">
+      <c r="V9" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="W8" s="15" t="s">
+      <c r="W9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="X8" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="33"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="37"/>
     </row>
-    <row r="9" spans="1:27" ht="15" thickTop="1"/>
-    <row r="11" spans="1:27">
-      <c r="A11" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+    <row r="10" spans="1:27" ht="15" thickTop="1">
+      <c r="O10" s="8"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="20"/>
+      <c r="A12" s="20" t="s">
+        <v>31</v>
+      </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="F12" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
       <c r="H13" s="21"/>
       <c r="I13" s="21"/>
       <c r="J13" s="21"/>
     </row>
     <row r="14" spans="1:27">
       <c r="A14" s="21"/>
-      <c r="B14" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="21"/>
-      <c r="F14" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="21"/>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="53"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+    </row>
+    <row r="16" spans="1:27">
+      <c r="A16" s="21"/>
+      <c r="B16" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="42" t="s">
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="42"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="T6:X6"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:X7"/>
-    <mergeCell ref="P6:S6"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="T7:X7"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:X8"/>
+    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="Z7:Z9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{ED24C437-66CF-4628-A32D-BDE23416ECFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F5301D3-CB56-4D57-9BB9-979A30387459}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{ED24C437-66CF-4628-A32D-BDE23416ECFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7F083E-7F56-41DD-BB70-AF534979C472}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E31E48B5-560A-4B75-91E6-47685E8599C6}"/>
   </bookViews>
@@ -692,7 +692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -830,6 +830,15 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -856,15 +865,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -873,6 +873,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1371,46 +1377,46 @@
       <c r="A7" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="58" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="61" t="s">
+      <c r="E7" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="58" t="s">
+      <c r="J7" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="58" t="s">
+      <c r="K7" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="58" t="s">
+      <c r="L7" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="58" t="s">
+      <c r="M7" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="55" t="s">
+      <c r="N7" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="55" t="s">
+      <c r="O7" s="58" t="s">
         <v>14</v>
       </c>
       <c r="P7" s="50" t="s">
@@ -1429,7 +1435,7 @@
       <c r="Y7" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="Z7" s="61" t="s">
+      <c r="Z7" s="53" t="s">
         <v>18</v>
       </c>
       <c r="AA7" s="35" t="s">
@@ -1438,20 +1444,20 @@
     </row>
     <row r="8" spans="1:27" ht="15" thickBot="1">
       <c r="A8" s="66"/>
-      <c r="B8" s="62"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="36"/>
       <c r="D8" s="33"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="59"/>
+      <c r="O8" s="59"/>
       <c r="P8" s="38" t="s">
         <v>20</v>
       </c>
@@ -1474,25 +1480,25 @@
       <c r="W8" s="48"/>
       <c r="X8" s="49"/>
       <c r="Y8" s="33"/>
-      <c r="Z8" s="62"/>
+      <c r="Z8" s="54"/>
       <c r="AA8" s="36"/>
     </row>
     <row r="9" spans="1:27" ht="43.8" thickBot="1">
       <c r="A9" s="46"/>
-      <c r="B9" s="63"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="37"/>
       <c r="D9" s="34"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="57"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="60"/>
       <c r="P9" s="39"/>
       <c r="Q9" s="41"/>
       <c r="R9" s="41"/>
@@ -1511,11 +1517,66 @@
         <v>30</v>
       </c>
       <c r="Y9" s="34"/>
-      <c r="Z9" s="63"/>
+      <c r="Z9" s="55"/>
       <c r="AA9" s="37"/>
     </row>
     <row r="10" spans="1:27" ht="15" thickTop="1">
-      <c r="O10" s="8"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="67"/>
+      <c r="AA10" s="67"/>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="67"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="67"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="67"/>
+      <c r="Z11" s="67"/>
+      <c r="AA11" s="67"/>
     </row>
     <row r="12" spans="1:27">
       <c r="A12" s="20" t="s">
@@ -1559,32 +1620,32 @@
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="21"/>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="21"/>
-      <c r="F15" s="53" t="s">
+      <c r="F15" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="53"/>
+      <c r="G15" s="56"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="21"/>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
       <c r="E16" s="21"/>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="54"/>
+      <c r="G16" s="57"/>
       <c r="H16" s="24"/>
       <c r="I16" s="24"/>
       <c r="J16" s="24"/>

--- a/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{ED24C437-66CF-4628-A32D-BDE23416ECFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7F083E-7F56-41DD-BB70-AF534979C472}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{ED24C437-66CF-4628-A32D-BDE23416ECFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC97F82E-B482-46C1-9D40-775D3C414283}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E31E48B5-560A-4B75-91E6-47685E8599C6}"/>
   </bookViews>
@@ -317,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -685,6 +685,15 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -692,7 +701,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -758,86 +767,62 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -847,38 +832,74 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -896,10 +917,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1199,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734DFF48-CF26-42BE-975B-28ABE9130CF9}">
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.88671875" style="2" customWidth="1"/>
@@ -1317,10 +1334,10 @@
       <c r="AA4" s="4"/>
     </row>
     <row r="5" spans="1:27" ht="15.6">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="64"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
@@ -1374,136 +1391,136 @@
       <c r="AA6" s="4"/>
     </row>
     <row r="7" spans="1:27" ht="15" thickTop="1">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="65" t="s">
+      <c r="D7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="61" t="s">
+      <c r="H7" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="61" t="s">
+      <c r="J7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="61" t="s">
+      <c r="K7" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="61" t="s">
+      <c r="L7" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="61" t="s">
+      <c r="M7" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="58" t="s">
+      <c r="N7" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="58" t="s">
+      <c r="O7" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="50" t="s">
+      <c r="P7" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="29" t="s">
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="68"/>
+      <c r="T7" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="32" t="s">
+      <c r="U7" s="51"/>
+      <c r="V7" s="51"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="52"/>
+      <c r="Y7" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="Z7" s="53" t="s">
+      <c r="Z7" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AA7" s="35" t="s">
+      <c r="AA7" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" thickBot="1">
-      <c r="A8" s="66"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="38" t="s">
+      <c r="A8" s="39"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="40" t="s">
+      <c r="Q8" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="42" t="s">
+      <c r="R8" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="43" t="s">
+      <c r="S8" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="T8" s="45" t="s">
+      <c r="T8" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="U8" s="47" t="s">
+      <c r="U8" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="54"/>
-      <c r="AA8" s="36"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="43"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="41"/>
     </row>
     <row r="9" spans="1:27" ht="43.8" thickBot="1">
-      <c r="A9" s="46"/>
-      <c r="B9" s="55"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="46"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="56"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="40"/>
       <c r="U9" s="16" t="s">
         <v>29</v>
       </c>
@@ -1516,142 +1533,190 @@
       <c r="X9" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="55"/>
-      <c r="AA9" s="37"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="42"/>
     </row>
-    <row r="10" spans="1:27" ht="15" thickTop="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="67"/>
-      <c r="Q10" s="67"/>
-      <c r="R10" s="67"/>
-      <c r="S10" s="67"/>
-      <c r="T10" s="67"/>
-      <c r="U10" s="67"/>
-      <c r="V10" s="67"/>
-      <c r="W10" s="67"/>
-      <c r="X10" s="67"/>
-      <c r="Y10" s="67"/>
-      <c r="Z10" s="67"/>
-      <c r="AA10" s="67"/>
+    <row r="10" spans="1:27" ht="0.6" customHeight="1" thickTop="1">
+      <c r="A10" s="71"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="71"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="67"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67"/>
-      <c r="Q11" s="67"/>
-      <c r="R11" s="67"/>
-      <c r="S11" s="67"/>
-      <c r="T11" s="67"/>
-      <c r="U11" s="67"/>
-      <c r="V11" s="67"/>
-      <c r="W11" s="67"/>
-      <c r="X11" s="67"/>
-      <c r="Y11" s="67"/>
-      <c r="Z11" s="67"/>
-      <c r="AA11" s="67"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="69"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="69"/>
+      <c r="W11" s="69"/>
+      <c r="X11" s="69"/>
+      <c r="Y11" s="69"/>
+      <c r="Z11" s="69"/>
+      <c r="AA11" s="69"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="20"/>
+      <c r="A13" s="20" t="s">
+        <v>31</v>
+      </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="F13" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
       <c r="I13" s="21"/>
       <c r="J13" s="21"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
       <c r="H14" s="21"/>
       <c r="I14" s="21"/>
       <c r="J14" s="21"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="21"/>
-      <c r="B15" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
       <c r="E15" s="21"/>
-      <c r="F15" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="56"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="21"/>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="48"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="21"/>
+      <c r="B17" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="57" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="57"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="T7:X7"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:X8"/>
+    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
     <mergeCell ref="O7:O9"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="J7:J9"/>
@@ -1664,25 +1729,6 @@
     <mergeCell ref="G7:G9"/>
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="L7:L9"/>
-    <mergeCell ref="T7:X7"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:X8"/>
-    <mergeCell ref="P7:S7"/>
-    <mergeCell ref="Z7:Z9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alaca\OneDrive\Documents\LPC\GSO\Template 2025_06_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2427AF36-52BC-4A9B-91C1-733C18B97144}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFA4B06-4770-4517-A2C4-A5DAD9C087C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -607,7 +607,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -661,6 +661,33 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -679,9 +706,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -694,29 +718,36 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -734,10 +765,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1055,12 +1082,12 @@
     <col min="13" max="13" width="11.109375" style="17" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.21875" style="7" customWidth="1"/>
     <col min="15" max="15" width="12.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.6640625" style="8" customWidth="1"/>
-    <col min="18" max="18" width="15.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.6640625" style="45" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.6640625" style="45" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12.44140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5546875" style="45" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6.88671875" style="7" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.5546875" style="7" customWidth="1"/>
     <col min="26" max="26" width="13.21875" style="7" bestFit="1" customWidth="1"/>
@@ -1074,7 +1101,15 @@
     <col min="34" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+    </row>
     <row r="2" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9"/>
       <c r="C2" s="1"/>
@@ -1090,14 +1125,14 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
       <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="39"/>
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
       <c r="Z2" s="10"/>
@@ -1126,14 +1161,14 @@
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
       <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
       <c r="Z3" s="13"/>
@@ -1160,14 +1195,14 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
       <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
       <c r="Z4" s="10"/>
@@ -1182,16 +1217,37 @@
     <row r="5" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="14"/>
       <c r="C5" s="10"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
     </row>
     <row r="6" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="6"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
     </row>
     <row r="7" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="14"/>
       <c r="C7" s="10"/>
       <c r="D7" s="6"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
     </row>
     <row r="8" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
@@ -1199,156 +1255,170 @@
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="6"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41"/>
     </row>
     <row r="9" spans="2:33" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="15"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="41"/>
     </row>
     <row r="10" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="30" t="s">
+      <c r="K10" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="30" t="s">
+      <c r="L10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="30" t="s">
+      <c r="M10" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="30" t="s">
+      <c r="N10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="30" t="s">
+      <c r="O10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="P10" s="30" t="s">
+      <c r="P10" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="30" t="s">
+      <c r="Q10" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="30" t="s">
+      <c r="R10" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="30" t="s">
+      <c r="S10" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="T10" s="25" t="s">
+      <c r="T10" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25" t="s">
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="27" t="s">
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="AD10" s="27" t="s">
+      <c r="AD10" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="AE10" s="19" t="s">
+      <c r="AE10" s="28" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="36"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="22" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="U11" s="24" t="s">
+      <c r="U11" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="24" t="s">
+      <c r="V11" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="W11" s="22" t="s">
+      <c r="W11" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="X11" s="24" t="s">
+      <c r="X11" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="Y11" s="24" t="s">
+      <c r="Y11" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="20"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="36"/>
+      <c r="AE11" s="29"/>
     </row>
     <row r="12" spans="2:33" s="2" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="37"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="32"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="48"/>
+      <c r="X12" s="34"/>
       <c r="Y12" s="5" t="s">
         <v>28</v>
       </c>
@@ -1361,15 +1431,30 @@
       <c r="AB12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="21"/>
+      <c r="AC12" s="37"/>
+      <c r="AD12" s="37"/>
+      <c r="AE12" s="30"/>
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.3">
       <c r="AG13" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="AE10:AE12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X10:AB10"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:AB11"/>
+    <mergeCell ref="AC10:AC12"/>
+    <mergeCell ref="AD10:AD12"/>
+    <mergeCell ref="P10:P12"/>
+    <mergeCell ref="Q10:Q12"/>
+    <mergeCell ref="R10:R12"/>
+    <mergeCell ref="S10:S12"/>
+    <mergeCell ref="T10:W10"/>
     <mergeCell ref="O10:O12"/>
     <mergeCell ref="J10:J12"/>
     <mergeCell ref="K10:K12"/>
@@ -1384,30 +1469,18 @@
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="M10:M12"/>
     <mergeCell ref="N10:N12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="Q10:Q12"/>
-    <mergeCell ref="R10:R12"/>
-    <mergeCell ref="S10:S12"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="AE10:AE12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X10:AB10"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:AB11"/>
-    <mergeCell ref="AC10:AC12"/>
-    <mergeCell ref="AD10:AD12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1561,26 +1634,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1604,9 +1666,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alaca\OneDrive\Documents\LPC\GSO\Template 2025_06_02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Tempalte 2025_06_24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFA4B06-4770-4517-A2C4-A5DAD9C087C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{BFFA4B06-4770-4517-A2C4-A5DAD9C087C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAEE1FCC-E2F9-447D-9CE6-55DF9858E93F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -607,11 +607,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -622,17 +619,8 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -640,9 +628,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -657,66 +642,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -728,26 +653,122 @@
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1067,394 +1088,429 @@
   <dimension ref="B1:AG13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="9" style="7" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="8"/>
-    <col min="6" max="6" width="20.33203125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5546875" style="17" customWidth="1"/>
-    <col min="11" max="11" width="24.6640625" style="17" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.21875" style="7" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.6640625" style="45" customWidth="1"/>
-    <col min="18" max="18" width="15.109375" style="45" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.6640625" style="45" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="12.44140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5546875" style="45" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.5546875" style="7" customWidth="1"/>
-    <col min="26" max="26" width="13.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5546875" style="7" customWidth="1"/>
-    <col min="30" max="30" width="9.5546875" style="17" customWidth="1"/>
-    <col min="31" max="31" width="26.6640625" style="17" customWidth="1"/>
-    <col min="32" max="32" width="8.88671875" style="4"/>
-    <col min="33" max="33" width="9.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="2.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="9" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="12"/>
+    <col min="6" max="6" width="20.33203125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5546875" style="12" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" style="12" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.21875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.6640625" style="17" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.88671875" style="17" customWidth="1"/>
+    <col min="20" max="20" width="10" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" style="17" customWidth="1"/>
+    <col min="24" max="24" width="18.6640625" style="5" customWidth="1"/>
+    <col min="25" max="25" width="15.5546875" style="5" customWidth="1"/>
+    <col min="26" max="26" width="13.21875" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.33203125" style="5" customWidth="1"/>
+    <col min="28" max="28" width="10.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5546875" style="5" customWidth="1"/>
+    <col min="30" max="30" width="9.5546875" style="12" customWidth="1"/>
+    <col min="31" max="31" width="26.6640625" style="12" customWidth="1"/>
+    <col min="32" max="32" width="8.88671875" style="3"/>
+    <col min="33" max="33" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
+    <row r="1" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="51"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AC1" s="43"/>
     </row>
-    <row r="2" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="9"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
+    <row r="2" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
     </row>
-    <row r="3" spans="2:33" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="B3" s="11" t="s">
+    <row r="3" spans="2:33" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13"/>
-      <c r="AF3" s="13"/>
-      <c r="AG3" s="13"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="46"/>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
     </row>
-    <row r="4" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="14"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
-      <c r="AF4" s="10"/>
-      <c r="AG4" s="10"/>
+    <row r="4" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="45"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
     </row>
-    <row r="5" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="14"/>
-      <c r="C5" s="10"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
+    <row r="5" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AC5" s="47"/>
     </row>
-    <row r="6" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="6"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
+    <row r="6" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AC6" s="47"/>
     </row>
-    <row r="7" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="14"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="6"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
+    <row r="7" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AC7" s="47"/>
     </row>
-    <row r="8" spans="2:33" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="6"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="41"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AC8" s="47"/>
     </row>
-    <row r="9" spans="2:33" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="15"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
+    <row r="9" spans="2:33" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="10"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AC9" s="47"/>
     </row>
-    <row r="10" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="24" t="s">
+    <row r="10" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="O10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="P10" s="42" t="s">
+      <c r="P10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="42" t="s">
+      <c r="Q10" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="42" t="s">
+      <c r="R10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="42" t="s">
+      <c r="S10" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="T10" s="27" t="s">
+      <c r="T10" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27" t="s">
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="27"/>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="35" t="s">
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="26"/>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="26"/>
+      <c r="AC10" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="AD10" s="35" t="s">
+      <c r="AD10" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="AE10" s="28" t="s">
+      <c r="AE10" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="25"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="31" t="s">
+    <row r="11" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="41"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="U11" s="46" t="s">
+      <c r="U11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="46" t="s">
+      <c r="V11" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="W11" s="47" t="s">
+      <c r="W11" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="X11" s="33" t="s">
+      <c r="X11" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="Y11" s="33" t="s">
+      <c r="Y11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="36"/>
-      <c r="AE11" s="29"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="19"/>
     </row>
-    <row r="12" spans="2:33" s="2" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="26"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="32"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="48"/>
-      <c r="W12" s="48"/>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="5" t="s">
+    <row r="12" spans="2:33" s="1" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="42"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Z12" s="5" t="s">
+      <c r="Z12" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="AA12" s="5" t="s">
+      <c r="AA12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AB12" s="5" t="s">
+      <c r="AB12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="30"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="20"/>
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="AG13" s="16"/>
+      <c r="AG13" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AE10:AE12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X10:AB10"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:AB11"/>
-    <mergeCell ref="AC10:AC12"/>
-    <mergeCell ref="AD10:AD12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="Q10:Q12"/>
-    <mergeCell ref="R10:R12"/>
-    <mergeCell ref="S10:S12"/>
-    <mergeCell ref="T10:W10"/>
     <mergeCell ref="O10:O12"/>
     <mergeCell ref="J10:J12"/>
     <mergeCell ref="K10:K12"/>
@@ -1469,18 +1525,30 @@
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="M10:M12"/>
     <mergeCell ref="N10:N12"/>
+    <mergeCell ref="P10:P12"/>
+    <mergeCell ref="Q10:Q12"/>
+    <mergeCell ref="R10:R12"/>
+    <mergeCell ref="S10:S12"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="AE10:AE12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X10:AB10"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:AB11"/>
+    <mergeCell ref="AC10:AC12"/>
+    <mergeCell ref="AD10:AD12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1634,15 +1702,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1666,17 +1745,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianStructureAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Tempalte 2025_06_24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{BFFA4B06-4770-4517-A2C4-A5DAD9C087C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAEE1FCC-E2F9-447D-9CE6-55DF9858E93F}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{BFFA4B06-4770-4517-A2C4-A5DAD9C087C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEF28147-CC93-4D32-9D9E-C71C0B3653B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -160,26 +160,17 @@
     <definedName name="WeekStart">#REF!</definedName>
     <definedName name="WeekStartValue">IF(WeekStart="Monday",2,1)</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Custodian 
 Item 
@@ -317,6 +308,9 @@
   </si>
   <si>
     <t xml:space="preserve">Custodian: </t>
+  </si>
+  <si>
+    <t>Sub-Account / Articles</t>
   </si>
 </sst>
 </file>
@@ -607,7 +601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -656,6 +650,81 @@
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -680,9 +749,6 @@
     <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -698,76 +764,13 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1085,65 +1088,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C67B7F-8F2D-41F8-81D3-3B33F7991409}">
-  <dimension ref="B1:AG13"/>
+  <dimension ref="B1:AH13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="9" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="12"/>
-    <col min="6" max="6" width="20.33203125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5546875" style="12" customWidth="1"/>
-    <col min="11" max="11" width="24.6640625" style="12" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.21875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.6640625" style="17" customWidth="1"/>
-    <col min="18" max="18" width="15.109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.88671875" style="17" customWidth="1"/>
-    <col min="20" max="20" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.6640625" style="17" customWidth="1"/>
-    <col min="24" max="24" width="18.6640625" style="5" customWidth="1"/>
-    <col min="25" max="25" width="15.5546875" style="5" customWidth="1"/>
-    <col min="26" max="26" width="13.21875" style="54" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.33203125" style="5" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5546875" style="5" customWidth="1"/>
-    <col min="30" max="30" width="9.5546875" style="12" customWidth="1"/>
-    <col min="31" max="31" width="26.6640625" style="12" customWidth="1"/>
-    <col min="32" max="32" width="8.88671875" style="3"/>
-    <col min="33" max="33" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="8.88671875" style="3"/>
+    <col min="4" max="4" width="26.88671875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="12"/>
+    <col min="7" max="7" width="20.33203125" style="12" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5546875" style="12" customWidth="1"/>
+    <col min="12" max="12" width="24.6640625" style="12" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.21875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.6640625" style="17" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.88671875" style="17" customWidth="1"/>
+    <col min="21" max="21" width="10" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.6640625" style="17" customWidth="1"/>
+    <col min="25" max="25" width="18.6640625" style="5" customWidth="1"/>
+    <col min="26" max="26" width="15.5546875" style="5" customWidth="1"/>
+    <col min="27" max="27" width="13.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.33203125" style="5" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.5546875" style="5" customWidth="1"/>
+    <col min="31" max="31" width="9.5546875" style="12" customWidth="1"/>
+    <col min="32" max="32" width="26.6640625" style="12" customWidth="1"/>
+    <col min="33" max="33" width="8.88671875" style="3"/>
+    <col min="34" max="34" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="51"/>
-      <c r="O1" s="13"/>
+    <row r="1" spans="2:34" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="26"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
       <c r="S1" s="13"/>
-      <c r="U1" s="13"/>
+      <c r="T1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AC1" s="43"/>
+      <c r="X1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AD1" s="18"/>
     </row>
-    <row r="2" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="6"/>
+    <row r="2" spans="2:34" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="9"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -1152,63 +1157,65 @@
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="14"/>
+      <c r="O2" s="6"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="6"/>
       <c r="V2" s="14"/>
       <c r="W2" s="14"/>
-      <c r="X2" s="6"/>
+      <c r="X2" s="14"/>
       <c r="Y2" s="6"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="14"/>
       <c r="AB2" s="6"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="20"/>
       <c r="AE2" s="6"/>
       <c r="AF2" s="6"/>
       <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
     </row>
-    <row r="3" spans="2:33" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:34" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="7"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="8"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
-      <c r="O3" s="15"/>
+      <c r="O3" s="8"/>
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
       <c r="R3" s="15"/>
       <c r="S3" s="15"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="8"/>
       <c r="V3" s="15"/>
       <c r="W3" s="15"/>
-      <c r="X3" s="8"/>
+      <c r="X3" s="15"/>
       <c r="Y3" s="8"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="15"/>
       <c r="AB3" s="8"/>
-      <c r="AC3" s="46"/>
-      <c r="AD3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="21"/>
       <c r="AE3" s="8"/>
       <c r="AF3" s="8"/>
       <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
     </row>
-    <row r="4" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:34" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -1218,340 +1225,346 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="6"/>
+      <c r="K4" s="9"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
-      <c r="O4" s="14"/>
+      <c r="O4" s="6"/>
       <c r="P4" s="14"/>
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
       <c r="S4" s="14"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="6"/>
       <c r="V4" s="14"/>
       <c r="W4" s="14"/>
-      <c r="X4" s="6"/>
+      <c r="X4" s="14"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="14"/>
       <c r="AB4" s="6"/>
-      <c r="AC4" s="45"/>
-      <c r="AD4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="20"/>
       <c r="AE4" s="6"/>
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
     </row>
-    <row r="5" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:34" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
-      <c r="O5" s="16"/>
+      <c r="K5" s="10"/>
       <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
-      <c r="U5" s="16"/>
+      <c r="T5" s="16"/>
       <c r="V5" s="16"/>
       <c r="W5" s="16"/>
-      <c r="Z5" s="16"/>
-      <c r="AC5" s="47"/>
+      <c r="X5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AD5" s="22"/>
     </row>
-    <row r="6" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="10"/>
+    <row r="6" spans="2:34" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
-      <c r="O6" s="16"/>
+      <c r="K6" s="10"/>
       <c r="P6" s="16"/>
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
-      <c r="U6" s="16"/>
+      <c r="T6" s="16"/>
       <c r="V6" s="16"/>
       <c r="W6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AC6" s="47"/>
+      <c r="X6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AD6" s="22"/>
     </row>
-    <row r="7" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:34" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="10"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
-      <c r="O7" s="16"/>
+      <c r="K7" s="10"/>
       <c r="P7" s="16"/>
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
-      <c r="U7" s="16"/>
+      <c r="T7" s="16"/>
       <c r="V7" s="16"/>
       <c r="W7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AC7" s="47"/>
+      <c r="X7" s="16"/>
+      <c r="AA7" s="16"/>
+      <c r="AD7" s="22"/>
     </row>
-    <row r="8" spans="2:33" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:34" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="10"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
-      <c r="O8" s="16"/>
+      <c r="K8" s="10"/>
       <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
-      <c r="U8" s="16"/>
+      <c r="T8" s="16"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AC8" s="47"/>
+      <c r="X8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AD8" s="22"/>
     </row>
-    <row r="9" spans="2:33" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="10"/>
-      <c r="O9" s="16"/>
+    <row r="9" spans="2:34" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="10"/>
       <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
-      <c r="U9" s="16"/>
+      <c r="T9" s="16"/>
       <c r="V9" s="16"/>
       <c r="W9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AC9" s="47"/>
+      <c r="X9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AD9" s="22"/>
     </row>
-    <row r="10" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="40" t="s">
+    <row r="10" spans="2:34" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="F10" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="G10" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="H10" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="I10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="J10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="K10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="L10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="35" t="s">
+      <c r="M10" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="35" t="s">
+      <c r="N10" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="O10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="32" t="s">
+      <c r="P10" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="P10" s="32" t="s">
+      <c r="Q10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="32" t="s">
+      <c r="R10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="32" t="s">
+      <c r="S10" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="32" t="s">
+      <c r="T10" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="T10" s="26" t="s">
+      <c r="U10" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26" t="s">
+      <c r="V10" s="42"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="42"/>
+      <c r="Y10" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-      <c r="AC10" s="29" t="s">
+      <c r="Z10" s="42"/>
+      <c r="AA10" s="42"/>
+      <c r="AB10" s="42"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="AD10" s="29" t="s">
+      <c r="AE10" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="AE10" s="18" t="s">
+      <c r="AF10" s="43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="41"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
+    <row r="11" spans="2:34" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="36"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="57"/>
       <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="36"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="21" t="s">
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="U11" s="23" t="s">
+      <c r="V11" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="23" t="s">
+      <c r="W11" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="W11" s="25" t="s">
+      <c r="X11" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="X11" s="27" t="s">
+      <c r="Y11" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="Y11" s="27" t="s">
+      <c r="Z11" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="27"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="30"/>
-      <c r="AE11" s="19"/>
+      <c r="AA11" s="51"/>
+      <c r="AB11" s="51"/>
+      <c r="AC11" s="51"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="44"/>
     </row>
-    <row r="12" spans="2:33" s="1" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="42"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
+    <row r="12" spans="2:34" s="1" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="37"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="58"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="37"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
       <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="4" t="s">
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Z12" s="55" t="s">
+      <c r="AA12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AA12" s="4" t="s">
+      <c r="AB12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AB12" s="4" t="s">
+      <c r="AC12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AC12" s="31"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="20"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="45"/>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="AG13" s="11"/>
+    <row r="13" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="AH13" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="O10:O12"/>
-    <mergeCell ref="J10:J12"/>
+  <mergeCells count="30">
+    <mergeCell ref="AF10:AF12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Z11:AC11"/>
+    <mergeCell ref="AD10:AD12"/>
+    <mergeCell ref="AE10:AE12"/>
+    <mergeCell ref="Q10:Q12"/>
+    <mergeCell ref="R10:R12"/>
+    <mergeCell ref="S10:S12"/>
+    <mergeCell ref="T10:T12"/>
+    <mergeCell ref="U10:X10"/>
+    <mergeCell ref="P10:P12"/>
     <mergeCell ref="K10:K12"/>
     <mergeCell ref="L10:L12"/>
+    <mergeCell ref="M10:M12"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="F10:F12"/>
     <mergeCell ref="G10:G12"/>
     <mergeCell ref="H10:H12"/>
     <mergeCell ref="I10:I12"/>
-    <mergeCell ref="M10:M12"/>
+    <mergeCell ref="J10:J12"/>
     <mergeCell ref="N10:N12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="Q10:Q12"/>
-    <mergeCell ref="R10:R12"/>
-    <mergeCell ref="S10:S12"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="AE10:AE12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X10:AB10"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:AB11"/>
-    <mergeCell ref="AC10:AC12"/>
-    <mergeCell ref="AD10:AD12"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="D10:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFE98289BC91294F829EFFD4DC549C76" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19972903a613892b44bc7de177b9930c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="24f70235-d7ab-48ae-872a-f5e45d821dca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="851bba6bbcd0ff4aaccc95eb8de2c74d" ns3:_="">
     <xsd:import namespace="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
@@ -1701,6 +1714,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1711,22 +1730,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E727EF53-D248-4693-8734-5FECE57054A9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1744,6 +1747,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
